--- a/filtered_data_2000.xlsx
+++ b/filtered_data_2000.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P501"/>
+  <dimension ref="A1:Q501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,11 @@
           <t>GDP_per_Worker</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Digital_growth_3yr</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -556,6 +561,9 @@
       </c>
       <c r="P2" t="n">
         <v>4682.874680923055</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.065497</v>
       </c>
     </row>
     <row r="3">
@@ -599,6 +607,9 @@
       <c r="P3" t="n">
         <v>5150.600627379068</v>
       </c>
+      <c r="Q3" t="n">
+        <v>0.260798</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -651,6 +662,9 @@
       <c r="P4" t="n">
         <v>5373.389449186601</v>
       </c>
+      <c r="Q4" t="n">
+        <v>0.308681</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -703,6 +717,9 @@
       <c r="P5" t="n">
         <v>5720.575845681512</v>
       </c>
+      <c r="Q5" t="n">
+        <v>0.857803</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -754,6 +771,9 @@
       </c>
       <c r="P6" t="n">
         <v>6091.475239709244</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.094592</v>
       </c>
     </row>
     <row r="7">
@@ -805,6 +825,9 @@
       <c r="P7" t="n">
         <v>6485.490395127829</v>
       </c>
+      <c r="Q7" t="n">
+        <v>5.653809</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -855,6 +878,9 @@
       <c r="P8" t="n">
         <v>6974.418417869608</v>
       </c>
+      <c r="Q8" t="n">
+        <v>8.63809</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -905,6 +931,9 @@
       <c r="P9" t="n">
         <v>7548.672416725892</v>
       </c>
+      <c r="Q9" t="n">
+        <v>12.61571</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -955,6 +984,9 @@
       <c r="P10" t="n">
         <v>8208.096404225411</v>
       </c>
+      <c r="Q10" t="n">
+        <v>17.81611</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1007,6 +1039,9 @@
       <c r="P11" t="n">
         <v>8119.745215512634</v>
       </c>
+      <c r="Q11" t="n">
+        <v>31.59001</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1059,6 +1094,9 @@
       <c r="P12" t="n">
         <v>8281.773584731</v>
       </c>
+      <c r="Q12" t="n">
+        <v>29.9639</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1111,6 +1149,9 @@
       <c r="P13" t="n">
         <v>7760.062619766152</v>
       </c>
+      <c r="Q13" t="n">
+        <v>23.14</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1163,6 +1204,9 @@
       <c r="P14" t="n">
         <v>8189.01339329104</v>
       </c>
+      <c r="Q14" t="n">
+        <v>8.199999999999996</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1215,6 +1259,9 @@
       <c r="P15" t="n">
         <v>9016.350164352663</v>
       </c>
+      <c r="Q15" t="n">
+        <v>6.799999999999997</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1267,6 +1314,9 @@
       <c r="P16" t="n">
         <v>9018.337379637096</v>
       </c>
+      <c r="Q16" t="n">
+        <v>7.299999999999997</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1319,6 +1369,9 @@
       <c r="P17" t="n">
         <v>8856.919897392136</v>
       </c>
+      <c r="Q17" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1371,6 +1424,9 @@
       <c r="P18" t="n">
         <v>8883.151646287019</v>
       </c>
+      <c r="Q18" t="n">
+        <v>7.800000000000004</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1423,6 +1479,9 @@
       <c r="P19" t="n">
         <v>9029.893568158919</v>
       </c>
+      <c r="Q19" t="n">
+        <v>8.100000000000001</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1475,6 +1534,9 @@
       <c r="P20" t="n">
         <v>9157.292305726854</v>
       </c>
+      <c r="Q20" t="n">
+        <v>8.500000000000007</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1527,6 +1589,9 @@
       <c r="P21" t="n">
         <v>9199.588561361375</v>
       </c>
+      <c r="Q21" t="n">
+        <v>8.950399999999995</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1579,6 +1644,9 @@
       <c r="P22" t="n">
         <v>9311.889804815022</v>
       </c>
+      <c r="Q22" t="n">
+        <v>9.837700000000005</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1631,6 +1699,9 @@
       <c r="P23" t="n">
         <v>10033.35751868563</v>
       </c>
+      <c r="Q23" t="n">
+        <v>13.9237</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1683,6 +1754,9 @@
       <c r="P24" t="n">
         <v>10354.65592057808</v>
       </c>
+      <c r="Q24" t="n">
+        <v>14.0633</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1734,6 +1808,9 @@
       </c>
       <c r="P25" t="n">
         <v>10860.93150077319</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>10.89789999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1777,6 +1854,9 @@
       <c r="P26" t="n">
         <v>11348.36331929434</v>
       </c>
+      <c r="Q26" t="n">
+        <v>2.811999999999998</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1826,6 +1906,9 @@
       </c>
       <c r="P27" t="n">
         <v>5419.552563782302</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.8114</v>
       </c>
     </row>
     <row r="28">
@@ -1871,6 +1954,9 @@
       <c r="P28" t="n">
         <v>5611.279282545735</v>
       </c>
+      <c r="Q28" t="n">
+        <v>4.22672</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1921,6 +2007,9 @@
       <c r="P29" t="n">
         <v>5851.283042725424</v>
       </c>
+      <c r="Q29" t="n">
+        <v>8.255970000000001</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1971,6 +2060,9 @@
       <c r="P30" t="n">
         <v>6232.604690428837</v>
       </c>
+      <c r="Q30" t="n">
+        <v>7.09057</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2021,6 +2113,9 @@
       <c r="P31" t="n">
         <v>6923.080035257899</v>
       </c>
+      <c r="Q31" t="n">
+        <v>12.89938</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2071,6 +2166,9 @@
       <c r="P32" t="n">
         <v>7556.084225220878</v>
       </c>
+      <c r="Q32" t="n">
+        <v>9.449029999999999</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2121,6 +2219,9 @@
       <c r="P33" t="n">
         <v>8289.716994730594</v>
       </c>
+      <c r="Q33" t="n">
+        <v>7.249029999999999</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2171,6 +2272,9 @@
       <c r="P34" t="n">
         <v>8971.282512405796</v>
       </c>
+      <c r="Q34" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2221,6 +2325,9 @@
       <c r="P35" t="n">
         <v>9832.875043569049</v>
       </c>
+      <c r="Q35" t="n">
+        <v>4.800000000000001</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2271,6 +2378,9 @@
       <c r="P36" t="n">
         <v>9792.488612540721</v>
       </c>
+      <c r="Q36" t="n">
+        <v>11.23</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2321,6 +2431,9 @@
       <c r="P37" t="n">
         <v>10500.19754838572</v>
       </c>
+      <c r="Q37" t="n">
+        <v>12.1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2371,6 +2484,9 @@
       <c r="P38" t="n">
         <v>11046.64393840255</v>
       </c>
+      <c r="Q38" t="n">
+        <v>16.6489</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2421,6 +2537,9 @@
       <c r="P39" t="n">
         <v>11222.73676281062</v>
       </c>
+      <c r="Q39" t="n">
+        <v>19.48</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2471,6 +2590,9 @@
       <c r="P40" t="n">
         <v>11331.35528821756</v>
       </c>
+      <c r="Q40" t="n">
+        <v>22.37</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2521,6 +2643,9 @@
       <c r="P41" t="n">
         <v>11517.53708169412</v>
       </c>
+      <c r="Q41" t="n">
+        <v>19.3674</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2571,6 +2696,9 @@
       <c r="P42" t="n">
         <v>11078.01241432449</v>
       </c>
+      <c r="Q42" t="n">
+        <v>15.32040000000001</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2621,6 +2749,9 @@
       <c r="P43" t="n">
         <v>10808.10037383299</v>
       </c>
+      <c r="Q43" t="n">
+        <v>16.943</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2671,6 +2802,9 @@
       <c r="P44" t="n">
         <v>11110.29784333526</v>
       </c>
+      <c r="Q44" t="n">
+        <v>15.42010000000001</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2721,6 +2855,9 @@
       <c r="P45" t="n">
         <v>11518.5180134941</v>
       </c>
+      <c r="Q45" t="n">
+        <v>16.8995</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2771,6 +2908,9 @@
       <c r="P46" t="n">
         <v>11753.00207280176</v>
       </c>
+      <c r="Q46" t="n">
+        <v>11.67619999999999</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2821,6 +2961,9 @@
       <c r="P47" t="n">
         <v>11775.09345275651</v>
       </c>
+      <c r="Q47" t="n">
+        <v>10.6515</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2871,6 +3014,9 @@
       <c r="P48" t="n">
         <v>12167.77343539123</v>
       </c>
+      <c r="Q48" t="n">
+        <v>7.758499999999998</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2921,6 +3067,9 @@
       <c r="P49" t="n">
         <v>11674.66685236204</v>
       </c>
+      <c r="Q49" t="n">
+        <v>6.718100000000007</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2970,6 +3119,9 @@
       </c>
       <c r="P50" t="n">
         <v>12279.77427012583</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>6.424599999999998</v>
       </c>
     </row>
     <row r="51">
@@ -3013,6 +3165,9 @@
       <c r="P51" t="n">
         <v>12876.10816856014</v>
       </c>
+      <c r="Q51" t="n">
+        <v>7.37339999999999</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3056,6 +3211,9 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
         <v>6194.944891232686</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1.02356</v>
       </c>
     </row>
     <row r="53">
@@ -3095,6 +3253,9 @@
       <c r="P53" t="n">
         <v>6252.374624620448</v>
       </c>
+      <c r="Q53" t="n">
+        <v>1.05653</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3139,6 +3300,9 @@
       <c r="P54" t="n">
         <v>6497.071179523037</v>
       </c>
+      <c r="Q54" t="n">
+        <v>2.45427</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3185,6 +3349,9 @@
       <c r="P55" t="n">
         <v>6718.365478221775</v>
       </c>
+      <c r="Q55" t="n">
+        <v>2.88208</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3231,6 +3398,9 @@
       <c r="P56" t="n">
         <v>7174.107954849409</v>
       </c>
+      <c r="Q56" t="n">
+        <v>14.26847</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3279,6 +3449,9 @@
       <c r="P57" t="n">
         <v>7505.432398646328</v>
       </c>
+      <c r="Q57" t="n">
+        <v>18.67843</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3329,6 +3502,9 @@
       <c r="P58" t="n">
         <v>7937.64971934593</v>
       </c>
+      <c r="Q58" t="n">
+        <v>21.15736</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3379,6 +3555,9 @@
       <c r="P59" t="n">
         <v>8470.855322172207</v>
       </c>
+      <c r="Q59" t="n">
+        <v>12.451</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3429,6 +3608,9 @@
       <c r="P60" t="n">
         <v>9051.904412951444</v>
       </c>
+      <c r="Q60" t="n">
+        <v>13.3333</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3479,6 +3661,9 @@
       <c r="P61" t="n">
         <v>8942.213373272207</v>
       </c>
+      <c r="Q61" t="n">
+        <v>12.6176</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3529,6 +3714,9 @@
       <c r="P62" t="n">
         <v>9186.283936951437</v>
       </c>
+      <c r="Q62" t="n">
+        <v>14.83</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3579,6 +3767,9 @@
       <c r="P63" t="n">
         <v>9453.373133785553</v>
       </c>
+      <c r="Q63" t="n">
+        <v>9.227700000000006</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3629,6 +3820,9 @@
       <c r="P64" t="n">
         <v>9573.541050836524</v>
       </c>
+      <c r="Q64" t="n">
+        <v>7.3245</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3679,6 +3873,9 @@
       <c r="P65" t="n">
         <v>9959.905410653091</v>
       </c>
+      <c r="Q65" t="n">
+        <v>5.771299999999997</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3729,6 +3926,9 @@
       <c r="P66" t="n">
         <v>10222.19123766867</v>
       </c>
+      <c r="Q66" t="n">
+        <v>6.030000000000001</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3779,6 +3979,9 @@
       <c r="P67" t="n">
         <v>10814.16944570564</v>
       </c>
+      <c r="Q67" t="n">
+        <v>7.535499999999999</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3829,6 +4032,9 @@
       <c r="P68" t="n">
         <v>11336.52959680517</v>
       </c>
+      <c r="Q68" t="n">
+        <v>11.73520000000001</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3879,6 +4085,9 @@
       <c r="P69" t="n">
         <v>11886.96064991614</v>
       </c>
+      <c r="Q69" t="n">
+        <v>14.97429999999999</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3929,6 +4138,9 @@
       <c r="P70" t="n">
         <v>12539.88769279386</v>
       </c>
+      <c r="Q70" t="n">
+        <v>17.52009999999999</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3979,6 +4191,9 @@
       <c r="P71" t="n">
         <v>13130.69209652729</v>
       </c>
+      <c r="Q71" t="n">
+        <v>9.689799999999991</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4029,6 +4244,9 @@
       <c r="P72" t="n">
         <v>13029.91848884734</v>
       </c>
+      <c r="Q72" t="n">
+        <v>8.319800000000001</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4079,6 +4297,9 @@
       <c r="P73" t="n">
         <v>14196.7287160727</v>
       </c>
+      <c r="Q73" t="n">
+        <v>5.556100000000001</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4129,6 +4350,9 @@
       <c r="P74" t="n">
         <v>14955.75591745051</v>
       </c>
+      <c r="Q74" t="n">
+        <v>8.899200000000008</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4178,6 +4402,9 @@
       </c>
       <c r="P75" t="n">
         <v>15137.95782798462</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>10.16540000000001</v>
       </c>
     </row>
     <row r="76">
@@ -4221,6 +4448,9 @@
       <c r="P76" t="n">
         <v>15633.35469674504</v>
       </c>
+      <c r="Q76" t="n">
+        <v>10.4247</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4272,6 +4502,9 @@
       </c>
       <c r="P77" t="n">
         <v>8826.50554151237</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>4.15092</v>
       </c>
     </row>
     <row r="78">
@@ -4319,6 +4552,9 @@
       <c r="P78" t="n">
         <v>9023.910796741146</v>
       </c>
+      <c r="Q78" t="n">
+        <v>5.7723</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4371,6 +4607,9 @@
       <c r="P79" t="n">
         <v>9808.84888847912</v>
       </c>
+      <c r="Q79" t="n">
+        <v>6.17</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4423,6 +4662,9 @@
       <c r="P80" t="n">
         <v>10520.37820515904</v>
       </c>
+      <c r="Q80" t="n">
+        <v>6.669079999999999</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4475,6 +4717,9 @@
       <c r="P81" t="n">
         <v>11075.09124146659</v>
       </c>
+      <c r="Q81" t="n">
+        <v>10.5177</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4527,6 +4772,9 @@
       <c r="P82" t="n">
         <v>12088.20950613285</v>
       </c>
+      <c r="Q82" t="n">
+        <v>10.89</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4579,6 +4827,9 @@
       <c r="P83" t="n">
         <v>12507.04194363954</v>
       </c>
+      <c r="Q83" t="n">
+        <v>15.05</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4631,6 +4882,9 @@
       <c r="P84" t="n">
         <v>13037.21777325423</v>
       </c>
+      <c r="Q84" t="n">
+        <v>15.51</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4683,6 +4937,9 @@
       <c r="P85" t="n">
         <v>13595.05660492696</v>
       </c>
+      <c r="Q85" t="n">
+        <v>19.7</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4735,6 +4992,9 @@
       <c r="P86" t="n">
         <v>13417.9227887245</v>
       </c>
+      <c r="Q86" t="n">
+        <v>17.91</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4787,6 +5047,9 @@
       <c r="P87" t="n">
         <v>13883.97151559861</v>
       </c>
+      <c r="Q87" t="n">
+        <v>12.59</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4839,6 +5102,9 @@
       <c r="P88" t="n">
         <v>14533.6024921541</v>
       </c>
+      <c r="Q88" t="n">
+        <v>8.309999999999995</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4891,6 +5157,9 @@
       <c r="P89" t="n">
         <v>14562.28905267106</v>
       </c>
+      <c r="Q89" t="n">
+        <v>6.899999999999999</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4943,6 +5212,9 @@
       <c r="P90" t="n">
         <v>14588.00663456967</v>
       </c>
+      <c r="Q90" t="n">
+        <v>6.831500000000005</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4995,6 +5267,9 @@
       <c r="P91" t="n">
         <v>14921.72714565422</v>
       </c>
+      <c r="Q91" t="n">
+        <v>7.510400000000004</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5047,6 +5322,9 @@
       <c r="P92" t="n">
         <v>15574.58428412743</v>
       </c>
+      <c r="Q92" t="n">
+        <v>4.756300000000003</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5099,6 +5377,9 @@
       <c r="P93" t="n">
         <v>16552.37639867856</v>
       </c>
+      <c r="Q93" t="n">
+        <v>6.763999999999996</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5151,6 +5432,9 @@
       <c r="P94" t="n">
         <v>16610.16465551967</v>
       </c>
+      <c r="Q94" t="n">
+        <v>7.919699999999999</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5203,6 +5487,9 @@
       <c r="P95" t="n">
         <v>17322.86110964629</v>
       </c>
+      <c r="Q95" t="n">
+        <v>8.125699999999995</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5255,6 +5542,9 @@
       <c r="P96" t="n">
         <v>17855.43319258787</v>
       </c>
+      <c r="Q96" t="n">
+        <v>8.121500000000005</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5307,6 +5597,9 @@
       <c r="P97" t="n">
         <v>17722.18532611191</v>
       </c>
+      <c r="Q97" t="n">
+        <v>6.752399999999994</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5359,6 +5652,9 @@
       <c r="P98" t="n">
         <v>19390.71014000487</v>
       </c>
+      <c r="Q98" t="n">
+        <v>10.4894</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5411,6 +5707,9 @@
       <c r="P99" t="n">
         <v>19825.82869576402</v>
       </c>
+      <c r="Q99" t="n">
+        <v>11.1799</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5462,6 +5761,9 @@
       </c>
       <c r="P100" t="n">
         <v>20195.26771505589</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>10.22710000000001</v>
       </c>
     </row>
     <row r="101">
@@ -5507,6 +5809,9 @@
       <c r="P101" t="n">
         <v>20815.4174915648</v>
       </c>
+      <c r="Q101" t="n">
+        <v>7.167599999999993</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5558,6 +5863,9 @@
       </c>
       <c r="P102" t="n">
         <v>20307.01566809639</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>4.91488</v>
       </c>
     </row>
     <row r="103">
@@ -5605,6 +5913,9 @@
       <c r="P103" t="n">
         <v>21879.18591269238</v>
       </c>
+      <c r="Q103" t="n">
+        <v>8.288600000000001</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5657,6 +5968,9 @@
       <c r="P104" t="n">
         <v>23282.44260304726</v>
       </c>
+      <c r="Q104" t="n">
+        <v>13.35</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5709,6 +6023,9 @@
       <c r="P105" t="n">
         <v>24493.10753921969</v>
       </c>
+      <c r="Q105" t="n">
+        <v>16.10512</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5761,6 +6078,9 @@
       <c r="P106" t="n">
         <v>24886.26026854755</v>
       </c>
+      <c r="Q106" t="n">
+        <v>19.3514</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5813,6 +6133,9 @@
       <c r="P107" t="n">
         <v>26001.22260874957</v>
       </c>
+      <c r="Q107" t="n">
+        <v>15.38</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5865,6 +6188,9 @@
       <c r="P108" t="n">
         <v>27549.21652481809</v>
       </c>
+      <c r="Q108" t="n">
+        <v>15.23</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5917,6 +6243,9 @@
       <c r="P109" t="n">
         <v>28480.51761059338</v>
       </c>
+      <c r="Q109" t="n">
+        <v>10.53</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5969,6 +6298,9 @@
       <c r="P110" t="n">
         <v>28897.95976867239</v>
       </c>
+      <c r="Q110" t="n">
+        <v>11.1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6021,6 +6353,9 @@
       <c r="P111" t="n">
         <v>26948.77309376017</v>
       </c>
+      <c r="Q111" t="n">
+        <v>12.6</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6073,6 +6408,9 @@
       <c r="P112" t="n">
         <v>26888.40808601375</v>
       </c>
+      <c r="Q112" t="n">
+        <v>15.11</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6125,6 +6463,9 @@
       <c r="P113" t="n">
         <v>27311.28086298616</v>
       </c>
+      <c r="Q113" t="n">
+        <v>13.55</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6177,6 +6518,9 @@
       <c r="P114" t="n">
         <v>27013.6296084918</v>
       </c>
+      <c r="Q114" t="n">
+        <v>11.36</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6229,6 +6573,9 @@
       <c r="P115" t="n">
         <v>27389.97242911411</v>
       </c>
+      <c r="Q115" t="n">
+        <v>10.19760000000001</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6281,6 +6628,9 @@
       <c r="P116" t="n">
         <v>26624.2170483696</v>
       </c>
+      <c r="Q116" t="n">
+        <v>10.7779</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6333,6 +6683,9 @@
       <c r="P117" t="n">
         <v>27330.84237375463</v>
       </c>
+      <c r="Q117" t="n">
+        <v>7.905000000000001</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6385,6 +6738,9 @@
       <c r="P118" t="n">
         <v>29381.69729605784</v>
       </c>
+      <c r="Q118" t="n">
+        <v>5.949699999999993</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6437,6 +6793,9 @@
       <c r="P119" t="n">
         <v>30667.97919208664</v>
       </c>
+      <c r="Q119" t="n">
+        <v>-1.471699999999998</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6489,6 +6848,9 @@
       <c r="P120" t="n">
         <v>32240.47358081021</v>
       </c>
+      <c r="Q120" t="n">
+        <v>5.449600000000004</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6541,6 +6903,9 @@
       <c r="P121" t="n">
         <v>33589.38624407438</v>
       </c>
+      <c r="Q121" t="n">
+        <v>6.382500000000007</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6593,6 +6958,9 @@
       <c r="P122" t="n">
         <v>31038.67276106305</v>
       </c>
+      <c r="Q122" t="n">
+        <v>11.2247</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6645,6 +7013,9 @@
       <c r="P123" t="n">
         <v>34634.21535475292</v>
       </c>
+      <c r="Q123" t="n">
+        <v>5.959400000000002</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6697,6 +7068,9 @@
       <c r="P124" t="n">
         <v>36807.77515806313</v>
       </c>
+      <c r="Q124" t="n">
+        <v>2.991799999999998</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6748,6 +7122,9 @@
       </c>
       <c r="P125" t="n">
         <v>38217.86340718007</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>4.920300000000012</v>
       </c>
     </row>
     <row r="126">
@@ -6791,6 +7168,9 @@
       <c r="P126" t="n">
         <v>39637.08026871159</v>
       </c>
+      <c r="Q126" t="n">
+        <v>2.378399999999999</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6840,6 +7220,9 @@
       </c>
       <c r="P127" t="n">
         <v>34943.77007452814</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>10.8754</v>
       </c>
     </row>
     <row r="128">
@@ -6885,6 +7268,9 @@
       <c r="P128" t="n">
         <v>34568.93632808307</v>
       </c>
+      <c r="Q128" t="n">
+        <v>9.928799999999999</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6935,6 +7321,9 @@
       <c r="P129" t="n">
         <v>35086.09213229077</v>
       </c>
+      <c r="Q129" t="n">
+        <v>17.02</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6985,6 +7374,9 @@
       <c r="P130" t="n">
         <v>34495.48023789631</v>
       </c>
+      <c r="Q130" t="n">
+        <v>14.8346</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7037,6 +7429,9 @@
       <c r="P131" t="n">
         <v>35248.50214836357</v>
       </c>
+      <c r="Q131" t="n">
+        <v>15.0112</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7089,6 +7484,9 @@
       <c r="P132" t="n">
         <v>36043.21739452991</v>
       </c>
+      <c r="Q132" t="n">
+        <v>4.490000000000002</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7141,6 +7539,9 @@
       <c r="P133" t="n">
         <v>36801.16103191789</v>
       </c>
+      <c r="Q133" t="n">
+        <v>5.739999999999998</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7193,6 +7594,9 @@
       <c r="P134" t="n">
         <v>37410.77140278424</v>
       </c>
+      <c r="Q134" t="n">
+        <v>6.940000000000005</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7245,6 +7649,9 @@
       <c r="P135" t="n">
         <v>37924.78740690316</v>
       </c>
+      <c r="Q135" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7297,6 +7704,9 @@
       <c r="P136" t="n">
         <v>36283.04755959561</v>
       </c>
+      <c r="Q136" t="n">
+        <v>13.98</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7349,6 +7759,9 @@
       <c r="P137" t="n">
         <v>36008.8702235302</v>
       </c>
+      <c r="Q137" t="n">
+        <v>12.22</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7401,6 +7814,9 @@
       <c r="P138" t="n">
         <v>35615.12945296465</v>
       </c>
+      <c r="Q138" t="n">
+        <v>14.5499</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7453,6 +7869,9 @@
       <c r="P139" t="n">
         <v>33628.78039796506</v>
       </c>
+      <c r="Q139" t="n">
+        <v>10.8799</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7505,6 +7924,9 @@
       <c r="P140" t="n">
         <v>30856.36529482546</v>
       </c>
+      <c r="Q140" t="n">
+        <v>12.4648</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7557,6 +7979,9 @@
       <c r="P141" t="n">
         <v>29529.62178016586</v>
       </c>
+      <c r="Q141" t="n">
+        <v>12.46879999999999</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7609,6 +8034,9 @@
       <c r="P142" t="n">
         <v>30285.01562504468</v>
       </c>
+      <c r="Q142" t="n">
+        <v>11.0258</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7661,6 +8089,9 @@
       <c r="P143" t="n">
         <v>32000.74943753002</v>
       </c>
+      <c r="Q143" t="n">
+        <v>10.44539999999999</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7713,6 +8144,9 @@
       <c r="P144" t="n">
         <v>33054.97574770104</v>
       </c>
+      <c r="Q144" t="n">
+        <v>11.4145</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7765,6 +8199,9 @@
       <c r="P145" t="n">
         <v>34138.00334472548</v>
       </c>
+      <c r="Q145" t="n">
+        <v>12.7179</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7817,6 +8254,9 @@
       <c r="P146" t="n">
         <v>35301.92896799753</v>
       </c>
+      <c r="Q146" t="n">
+        <v>10.1634</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7869,6 +8309,9 @@
       <c r="P147" t="n">
         <v>33959.37461259764</v>
       </c>
+      <c r="Q147" t="n">
+        <v>10.0587</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7921,6 +8364,9 @@
       <c r="P148" t="n">
         <v>36994.58805862629</v>
       </c>
+      <c r="Q148" t="n">
+        <v>6.325900000000004</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7973,6 +8419,9 @@
       <c r="P149" t="n">
         <v>38595.0195829645</v>
       </c>
+      <c r="Q149" t="n">
+        <v>3.537400000000005</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8024,6 +8473,9 @@
       </c>
       <c r="P150" t="n">
         <v>39111.73703724563</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0.4192000000000036</v>
       </c>
     </row>
     <row r="151">
@@ -8065,6 +8517,7 @@
       <c r="P151" t="n">
         <v>40160.88458188847</v>
       </c>
+      <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8116,6 +8569,9 @@
       </c>
       <c r="P152" t="n">
         <v>24854.32123975403</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>6.860530000000001</v>
       </c>
     </row>
     <row r="153">
@@ -8163,6 +8619,9 @@
       <c r="P153" t="n">
         <v>25726.00678872777</v>
       </c>
+      <c r="Q153" t="n">
+        <v>10.7972</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8215,6 +8674,9 @@
       <c r="P154" t="n">
         <v>26137.06666592613</v>
       </c>
+      <c r="Q154" t="n">
+        <v>17.1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8267,6 +8729,9 @@
       <c r="P155" t="n">
         <v>27036.55707292584</v>
       </c>
+      <c r="Q155" t="n">
+        <v>24.51947</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8319,6 +8784,9 @@
       <c r="P156" t="n">
         <v>28326.16913192387</v>
       </c>
+      <c r="Q156" t="n">
+        <v>20.8028</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8371,6 +8839,9 @@
       <c r="P157" t="n">
         <v>29889.20302617412</v>
       </c>
+      <c r="Q157" t="n">
+        <v>11.34</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8423,6 +8894,9 @@
       <c r="P158" t="n">
         <v>31763.33171832963</v>
       </c>
+      <c r="Q158" t="n">
+        <v>13.63</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8475,6 +8949,9 @@
       <c r="P159" t="n">
         <v>33527.6810147272</v>
       </c>
+      <c r="Q159" t="n">
+        <v>16.43</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8527,6 +9004,9 @@
       <c r="P160" t="n">
         <v>34305.92386204701</v>
       </c>
+      <c r="Q160" t="n">
+        <v>27.7</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8579,6 +9059,9 @@
       <c r="P161" t="n">
         <v>32406.40879235354</v>
       </c>
+      <c r="Q161" t="n">
+        <v>16.50000000000001</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8631,6 +9114,9 @@
       <c r="P162" t="n">
         <v>33371.86745715995</v>
       </c>
+      <c r="Q162" t="n">
+        <v>16.88999999999999</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8683,6 +9169,9 @@
       <c r="P163" t="n">
         <v>34013.77695322211</v>
       </c>
+      <c r="Q163" t="n">
+        <v>7.519999999999996</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8735,6 +9224,9 @@
       <c r="P164" t="n">
         <v>33554.17318179154</v>
       </c>
+      <c r="Q164" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8787,6 +9279,9 @@
       <c r="P165" t="n">
         <v>33246.56999041544</v>
       </c>
+      <c r="Q165" t="n">
+        <v>5.290400000000005</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8839,6 +9334,9 @@
       <c r="P166" t="n">
         <v>34016.78508063071</v>
       </c>
+      <c r="Q166" t="n">
+        <v>3.741700000000009</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8891,6 +9389,9 @@
       <c r="P167" t="n">
         <v>35646.63848766364</v>
       </c>
+      <c r="Q167" t="n">
+        <v>2.238799999999998</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8943,6 +9444,9 @@
       <c r="P168" t="n">
         <v>36295.83610902011</v>
       </c>
+      <c r="Q168" t="n">
+        <v>2.370800000000003</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8995,6 +9499,9 @@
       <c r="P169" t="n">
         <v>37988.67984162123</v>
       </c>
+      <c r="Q169" t="n">
+        <v>4.487499999999997</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9047,6 +9554,9 @@
       <c r="P170" t="n">
         <v>38814.92713847083</v>
       </c>
+      <c r="Q170" t="n">
+        <v>5.01939999999999</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9099,6 +9609,9 @@
       <c r="P171" t="n">
         <v>40275.15547252973</v>
       </c>
+      <c r="Q171" t="n">
+        <v>4.3857</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9151,6 +9664,9 @@
       <c r="P172" t="n">
         <v>38508.86372369828</v>
       </c>
+      <c r="Q172" t="n">
+        <v>2.619699999999995</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9203,6 +9719,9 @@
       <c r="P173" t="n">
         <v>40831.83953152229</v>
       </c>
+      <c r="Q173" t="n">
+        <v>1.982399999999998</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9254,6 +9773,9 @@
       </c>
       <c r="P174" t="n">
         <v>40994.05451536184</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>3.673199999999994</v>
       </c>
     </row>
     <row r="175">
@@ -9304,6 +9826,9 @@
       </c>
       <c r="P175" t="n">
         <v>39741.71315668939</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>4.655100000000004</v>
       </c>
     </row>
     <row r="176">
@@ -9349,6 +9874,9 @@
       <c r="P176" t="n">
         <v>40150.45725234297</v>
       </c>
+      <c r="Q176" t="n">
+        <v>5.017200000000003</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9400,6 +9928,9 @@
       </c>
       <c r="P177" t="n">
         <v>20623.89195510726</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>22.867</v>
       </c>
     </row>
     <row r="178">
@@ -9447,6 +9978,9 @@
       <c r="P178" t="n">
         <v>22194.2573204978</v>
       </c>
+      <c r="Q178" t="n">
+        <v>20.7275</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9499,6 +10033,9 @@
       <c r="P179" t="n">
         <v>24168.99726075589</v>
       </c>
+      <c r="Q179" t="n">
+        <v>27.02</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9551,6 +10088,9 @@
       <c r="P180" t="n">
         <v>25209.59155477542</v>
       </c>
+      <c r="Q180" t="n">
+        <v>16.743</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9603,6 +10143,9 @@
       <c r="P181" t="n">
         <v>26842.40440999396</v>
       </c>
+      <c r="Q181" t="n">
+        <v>21.6725</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9655,6 +10198,9 @@
       <c r="P182" t="n">
         <v>29586.86129198284</v>
       </c>
+      <c r="Q182" t="n">
+        <v>19.93</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9707,6 +10253,9 @@
       <c r="P183" t="n">
         <v>31555.13779908744</v>
       </c>
+      <c r="Q183" t="n">
+        <v>18.19</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9759,6 +10308,9 @@
       <c r="P184" t="n">
         <v>34047.93055589254</v>
       </c>
+      <c r="Q184" t="n">
+        <v>12.98999999999999</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9811,6 +10363,9 @@
       <c r="P185" t="n">
         <v>32061.79978333229</v>
       </c>
+      <c r="Q185" t="n">
+        <v>9.129999999999995</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9863,6 +10418,9 @@
       <c r="P186" t="n">
         <v>27651.86084264613</v>
       </c>
+      <c r="Q186" t="n">
+        <v>8.990000000000002</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9915,6 +10473,9 @@
       <c r="P187" t="n">
         <v>28579.11907062378</v>
       </c>
+      <c r="Q187" t="n">
+        <v>7.909999999999997</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9967,6 +10528,9 @@
       <c r="P188" t="n">
         <v>30541.36181697113</v>
       </c>
+      <c r="Q188" t="n">
+        <v>5.920000000000002</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10019,6 +10583,9 @@
       <c r="P189" t="n">
         <v>31835.53467839845</v>
       </c>
+      <c r="Q189" t="n">
+        <v>5.889899999999997</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10071,6 +10638,9 @@
       <c r="P190" t="n">
         <v>32558.58676860367</v>
       </c>
+      <c r="Q190" t="n">
+        <v>5.904300000000006</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10123,6 +10693,9 @@
       <c r="P191" t="n">
         <v>33893.97393246967</v>
       </c>
+      <c r="Q191" t="n">
+        <v>7.741500000000002</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10175,6 +10748,9 @@
       <c r="P192" t="n">
         <v>34135.29706913562</v>
       </c>
+      <c r="Q192" t="n">
+        <v>10.0198</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10227,6 +10803,9 @@
       <c r="P193" t="n">
         <v>34775.89057040327</v>
       </c>
+      <c r="Q193" t="n">
+        <v>7.235900000000001</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10279,6 +10858,9 @@
       <c r="P194" t="n">
         <v>36393.88241085661</v>
       </c>
+      <c r="Q194" t="n">
+        <v>3.861000000000004</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10331,6 +10913,9 @@
       <c r="P195" t="n">
         <v>37498.33592690459</v>
       </c>
+      <c r="Q195" t="n">
+        <v>0.9472999999999985</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10383,6 +10968,9 @@
       <c r="P196" t="n">
         <v>38991.40404011112</v>
       </c>
+      <c r="Q196" t="n">
+        <v>2.988699999999994</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10435,6 +11023,9 @@
       <c r="P197" t="n">
         <v>37866.91293124279</v>
       </c>
+      <c r="Q197" t="n">
+        <v>0.9557999999999964</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10487,6 +11078,9 @@
       <c r="P198" t="n">
         <v>40411.34170691458</v>
       </c>
+      <c r="Q198" t="n">
+        <v>1.622699999999995</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10539,6 +11133,9 @@
       <c r="P199" t="n">
         <v>38649.54034540316</v>
       </c>
+      <c r="Q199" t="n">
+        <v>1.291300000000007</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10590,6 +11187,9 @@
       </c>
       <c r="P200" t="n">
         <v>36502.95652666658</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>4.125100000000003</v>
       </c>
     </row>
     <row r="201">
@@ -10633,6 +11233,9 @@
       <c r="P201" t="n">
         <v>36371.42634541367</v>
       </c>
+      <c r="Q201" t="n">
+        <v>1.258300000000006</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10684,6 +11287,9 @@
       </c>
       <c r="P202" t="n">
         <v>41574.77752817293</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>7.28884</v>
       </c>
     </row>
     <row r="203">
@@ -10731,6 +11337,9 @@
       <c r="P203" t="n">
         <v>43854.19842845987</v>
       </c>
+      <c r="Q203" t="n">
+        <v>7.715</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10783,6 +11392,9 @@
       <c r="P204" t="n">
         <v>45413.73978824957</v>
       </c>
+      <c r="Q204" t="n">
+        <v>7.79</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10835,6 +11447,9 @@
       <c r="P205" t="n">
         <v>47453.82639944002</v>
       </c>
+      <c r="Q205" t="n">
+        <v>8.661160000000001</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10887,6 +11502,9 @@
       <c r="P206" t="n">
         <v>49151.38043893415</v>
       </c>
+      <c r="Q206" t="n">
+        <v>10.485</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10939,6 +11557,9 @@
       <c r="P207" t="n">
         <v>49349.8859303525</v>
       </c>
+      <c r="Q207" t="n">
+        <v>9.33</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10991,6 +11612,9 @@
       <c r="P208" t="n">
         <v>52002.37056904573</v>
       </c>
+      <c r="Q208" t="n">
+        <v>14.45</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11043,6 +11667,9 @@
       <c r="P209" t="n">
         <v>53761.08752507879</v>
       </c>
+      <c r="Q209" t="n">
+        <v>14.46</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -11095,6 +11722,9 @@
       <c r="P210" t="n">
         <v>53557.03237757817</v>
       </c>
+      <c r="Q210" t="n">
+        <v>14.2</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11147,6 +11777,9 @@
       <c r="P211" t="n">
         <v>50821.17988827697</v>
       </c>
+      <c r="Q211" t="n">
+        <v>10.15</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11199,6 +11832,9 @@
       <c r="P212" t="n">
         <v>47720.6288046266</v>
       </c>
+      <c r="Q212" t="n">
+        <v>8.519999999999996</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11251,6 +11887,9 @@
       <c r="P213" t="n">
         <v>43688.63376412969</v>
       </c>
+      <c r="Q213" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11303,6 +11942,9 @@
       <c r="P214" t="n">
         <v>40480.27380576998</v>
       </c>
+      <c r="Q214" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11355,6 +11997,9 @@
       <c r="P215" t="n">
         <v>40097.02123338804</v>
       </c>
+      <c r="Q215" t="n">
+        <v>15.4663</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11407,6 +12052,9 @@
       <c r="P216" t="n">
         <v>40915.84973765964</v>
       </c>
+      <c r="Q216" t="n">
+        <v>11.5573</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11459,6 +12107,9 @@
       <c r="P217" t="n">
         <v>41066.1023270611</v>
       </c>
+      <c r="Q217" t="n">
+        <v>11.76499999999999</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11511,6 +12162,9 @@
       <c r="P218" t="n">
         <v>41245.05024296641</v>
       </c>
+      <c r="Q218" t="n">
+        <v>9.221600000000002</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11563,6 +12217,9 @@
       <c r="P219" t="n">
         <v>42029.6508761074</v>
       </c>
+      <c r="Q219" t="n">
+        <v>6.685700000000004</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11615,6 +12272,9 @@
       <c r="P220" t="n">
         <v>43146.43667500049</v>
       </c>
+      <c r="Q220" t="n">
+        <v>5.403400000000005</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11667,6 +12327,9 @@
       <c r="P221" t="n">
         <v>44090.17494152994</v>
       </c>
+      <c r="Q221" t="n">
+        <v>6.583299999999994</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -11719,6 +12382,9 @@
       <c r="P222" t="n">
         <v>40703.2379569344</v>
       </c>
+      <c r="Q222" t="n">
+        <v>8.222799999999992</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -11771,6 +12437,9 @@
       <c r="P223" t="n">
         <v>44446.29595648003</v>
       </c>
+      <c r="Q223" t="n">
+        <v>6.255899999999997</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11823,6 +12492,9 @@
       <c r="P224" t="n">
         <v>46127.55673668285</v>
       </c>
+      <c r="Q224" t="n">
+        <v>7.499499999999998</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11874,6 +12546,9 @@
       </c>
       <c r="P225" t="n">
         <v>47202.03247728565</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>6.894400000000005</v>
       </c>
     </row>
     <row r="226">
@@ -11917,6 +12592,9 @@
       <c r="P226" t="n">
         <v>48329.45963288975</v>
       </c>
+      <c r="Q226" t="n">
+        <v>7.775400000000005</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11968,6 +12646,9 @@
       </c>
       <c r="P227" t="n">
         <v>21071.33794220363</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>5.05968</v>
       </c>
     </row>
     <row r="228">
@@ -12015,6 +12696,9 @@
       <c r="P228" t="n">
         <v>21757.13883280368</v>
       </c>
+      <c r="Q228" t="n">
+        <v>10.6386</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -12067,6 +12751,9 @@
       <c r="P229" t="n">
         <v>22656.24923987565</v>
       </c>
+      <c r="Q229" t="n">
+        <v>10.81</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -12119,6 +12806,9 @@
       <c r="P230" t="n">
         <v>23470.63406800077</v>
       </c>
+      <c r="Q230" t="n">
+        <v>14.63032</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -12171,6 +12861,9 @@
       <c r="P231" t="n">
         <v>24530.49544169621</v>
       </c>
+      <c r="Q231" t="n">
+        <v>13.2114</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -12223,6 +12916,9 @@
       <c r="P232" t="n">
         <v>25511.22969436273</v>
       </c>
+      <c r="Q232" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -12275,6 +12971,9 @@
       <c r="P233" t="n">
         <v>26455.8782830144</v>
       </c>
+      <c r="Q233" t="n">
+        <v>25.43</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -12327,6 +13026,9 @@
       <c r="P234" t="n">
         <v>26575.1093112141</v>
       </c>
+      <c r="Q234" t="n">
+        <v>25.56</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -12379,6 +13081,9 @@
       <c r="P235" t="n">
         <v>26907.53282255053</v>
       </c>
+      <c r="Q235" t="n">
+        <v>22.03</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -12431,6 +13136,9 @@
       <c r="P236" t="n">
         <v>25369.73930237659</v>
       </c>
+      <c r="Q236" t="n">
+        <v>14.94</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12483,6 +13191,9 @@
       <c r="P237" t="n">
         <v>25446.05032483039</v>
       </c>
+      <c r="Q237" t="n">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -12535,6 +13246,9 @@
       <c r="P238" t="n">
         <v>25846.23068816338</v>
       </c>
+      <c r="Q238" t="n">
+        <v>7.019999999999996</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -12587,6 +13301,9 @@
       <c r="P239" t="n">
         <v>25298.47058633778</v>
       </c>
+      <c r="Q239" t="n">
+        <v>8.579999999999998</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -12639,6 +13356,9 @@
       <c r="P240" t="n">
         <v>25612.19327871451</v>
       </c>
+      <c r="Q240" t="n">
+        <v>7.643900000000002</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -12691,6 +13411,9 @@
       <c r="P241" t="n">
         <v>26113.99647887575</v>
       </c>
+      <c r="Q241" t="n">
+        <v>7.633200000000002</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -12743,6 +13466,9 @@
       <c r="P242" t="n">
         <v>26598.68833610118</v>
       </c>
+      <c r="Q242" t="n">
+        <v>2.2547</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -12795,6 +13521,9 @@
       <c r="P243" t="n">
         <v>26845.51243510956</v>
       </c>
+      <c r="Q243" t="n">
+        <v>6.615499999999997</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -12847,6 +13576,9 @@
       <c r="P244" t="n">
         <v>27796.26235300956</v>
       </c>
+      <c r="Q244" t="n">
+        <v>1.097300000000004</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -12899,6 +13631,9 @@
       <c r="P245" t="n">
         <v>29153.94055262841</v>
       </c>
+      <c r="Q245" t="n">
+        <v>3.239699999999999</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -12951,6 +13686,9 @@
       <c r="P246" t="n">
         <v>30586.05286129285</v>
       </c>
+      <c r="Q246" t="n">
+        <v>1.112300000000005</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -13003,6 +13741,9 @@
       <c r="P247" t="n">
         <v>29339.12492059144</v>
       </c>
+      <c r="Q247" t="n">
+        <v>8.020699999999991</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -13055,6 +13796,9 @@
       <c r="P248" t="n">
         <v>31207.54463891322</v>
       </c>
+      <c r="Q248" t="n">
+        <v>12.5664</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -13106,6 +13850,9 @@
       </c>
       <c r="P249" t="n">
         <v>32237.31468696442</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>8.77109999999999</v>
       </c>
     </row>
     <row r="250">
@@ -13156,6 +13903,9 @@
       </c>
       <c r="P250" t="n">
         <v>31650.46185649935</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>6.678900000000013</v>
       </c>
     </row>
     <row r="251">
@@ -13199,6 +13949,9 @@
       <c r="P251" t="n">
         <v>31896.97713409973</v>
       </c>
+      <c r="Q251" t="n">
+        <v>5.138199999999998</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13250,6 +14003,9 @@
       </c>
       <c r="P252" t="n">
         <v>13705.93106490296</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>4.269060000000001</v>
       </c>
     </row>
     <row r="253">
@@ -13297,6 +14053,9 @@
       <c r="P253" t="n">
         <v>14578.5736161362</v>
       </c>
+      <c r="Q253" t="n">
+        <v>3.899350000000001</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -13349,6 +14108,9 @@
       <c r="P254" t="n">
         <v>15410.57257498957</v>
       </c>
+      <c r="Q254" t="n">
+        <v>17.55</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -13401,6 +14163,9 @@
       <c r="P255" t="n">
         <v>17003.67760329202</v>
       </c>
+      <c r="Q255" t="n">
+        <v>20.66094</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -13453,6 +14218,9 @@
       <c r="P256" t="n">
         <v>18472.93592091839</v>
       </c>
+      <c r="Q256" t="n">
+        <v>31.36065</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -13505,6 +14273,9 @@
       <c r="P257" t="n">
         <v>20723.49456074822</v>
       </c>
+      <c r="Q257" t="n">
+        <v>24.06</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -13557,6 +14328,9 @@
       <c r="P258" t="n">
         <v>22795.2447522977</v>
       </c>
+      <c r="Q258" t="n">
+        <v>26.65</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -13609,6 +14383,9 @@
       <c r="P259" t="n">
         <v>24774.13633111941</v>
       </c>
+      <c r="Q259" t="n">
+        <v>20.59</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -13661,6 +14438,9 @@
       <c r="P260" t="n">
         <v>23653.61073538537</v>
       </c>
+      <c r="Q260" t="n">
+        <v>17.41</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -13713,6 +14493,9 @@
       <c r="P261" t="n">
         <v>20692.01411624602</v>
       </c>
+      <c r="Q261" t="n">
+        <v>13.21</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -13765,6 +14548,9 @@
       <c r="P262" t="n">
         <v>20802.36307084666</v>
       </c>
+      <c r="Q262" t="n">
+        <v>9.25</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -13817,6 +14603,9 @@
       <c r="P263" t="n">
         <v>21963.86767533713</v>
       </c>
+      <c r="Q263" t="n">
+        <v>6.340000000000003</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -13869,6 +14658,9 @@
       <c r="P264" t="n">
         <v>23424.17958720453</v>
       </c>
+      <c r="Q264" t="n">
+        <v>6.279899999999998</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -13921,6 +14713,9 @@
       <c r="P265" t="n">
         <v>24381.48551319381</v>
       </c>
+      <c r="Q265" t="n">
+        <v>6.814399999999992</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -13973,6 +14768,9 @@
       <c r="P266" t="n">
         <v>25241.27273682809</v>
       </c>
+      <c r="Q266" t="n">
+        <v>6.076099999999997</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -14025,6 +14823,9 @@
       <c r="P267" t="n">
         <v>26141.88782061698</v>
       </c>
+      <c r="Q267" t="n">
+        <v>6.080699999999993</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -14077,6 +14878,9 @@
       <c r="P268" t="n">
         <v>27006.99294289384</v>
       </c>
+      <c r="Q268" t="n">
+        <v>4.607700000000008</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -14129,6 +14933,9 @@
       <c r="P269" t="n">
         <v>28058.90750000253</v>
       </c>
+      <c r="Q269" t="n">
+        <v>4.287999999999997</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -14181,6 +14988,9 @@
       <c r="P270" t="n">
         <v>29286.96316777839</v>
       </c>
+      <c r="Q270" t="n">
+        <v>4.37660000000001</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -14233,6 +15043,9 @@
       <c r="P271" t="n">
         <v>29851.03113593207</v>
       </c>
+      <c r="Q271" t="n">
+        <v>6.293399999999991</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -14285,6 +15098,9 @@
       <c r="P272" t="n">
         <v>28812.17663121092</v>
       </c>
+      <c r="Q272" t="n">
+        <v>8.783900000000003</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -14337,6 +15153,9 @@
       <c r="P273" t="n">
         <v>31846.45813659233</v>
       </c>
+      <c r="Q273" t="n">
+        <v>7.602399999999989</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14389,6 +15208,9 @@
       <c r="P274" t="n">
         <v>32021.90552084924</v>
       </c>
+      <c r="Q274" t="n">
+        <v>4.894600000000011</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -14440,6 +15262,9 @@
       </c>
       <c r="P275" t="n">
         <v>32851.43321131117</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>3.289900000000003</v>
       </c>
     </row>
     <row r="276">
@@ -14483,6 +15308,9 @@
       <c r="P276" t="n">
         <v>33062.59123660174</v>
       </c>
+      <c r="Q276" t="n">
+        <v>1.528000000000006</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14534,6 +15362,9 @@
       </c>
       <c r="P277" t="n">
         <v>13252.30735006709</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>5.44907</v>
       </c>
     </row>
     <row r="278">
@@ -14581,6 +15412,9 @@
       <c r="P278" t="n">
         <v>14453.80813397927</v>
       </c>
+      <c r="Q278" t="n">
+        <v>5.20936</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14633,6 +15467,9 @@
       <c r="P279" t="n">
         <v>15612.03765823372</v>
       </c>
+      <c r="Q279" t="n">
+        <v>14.77</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -14685,6 +15522,9 @@
       <c r="P280" t="n">
         <v>16696.6005605775</v>
       </c>
+      <c r="Q280" t="n">
+        <v>19.48293</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -14737,6 +15577,9 @@
       <c r="P281" t="n">
         <v>18789.94451700907</v>
       </c>
+      <c r="Q281" t="n">
+        <v>24.05064</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -14789,6 +15632,9 @@
       <c r="P282" t="n">
         <v>20754.27726432836</v>
       </c>
+      <c r="Q282" t="n">
+        <v>18.53</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -14841,6 +15687,9 @@
       <c r="P283" t="n">
         <v>22918.26658458027</v>
       </c>
+      <c r="Q283" t="n">
+        <v>17.99</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -14893,6 +15742,9 @@
       <c r="P284" t="n">
         <v>25464.32385488923</v>
       </c>
+      <c r="Q284" t="n">
+        <v>18.67</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -14945,6 +15797,9 @@
       <c r="P285" t="n">
         <v>26085.35110709062</v>
       </c>
+      <c r="Q285" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -14997,6 +15852,9 @@
       <c r="P286" t="n">
         <v>22096.05592113303</v>
       </c>
+      <c r="Q286" t="n">
+        <v>15.86</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -15049,6 +15907,9 @@
       <c r="P287" t="n">
         <v>22591.14020392905</v>
       </c>
+      <c r="Q287" t="n">
+        <v>12.22</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -15101,6 +15962,9 @@
       <c r="P288" t="n">
         <v>24211.50188062069</v>
       </c>
+      <c r="Q288" t="n">
+        <v>8.420000000000002</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -15153,6 +16017,9 @@
       <c r="P289" t="n">
         <v>25421.23924394263</v>
       </c>
+      <c r="Q289" t="n">
+        <v>7.470000000000006</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -15205,6 +16072,9 @@
       <c r="P290" t="n">
         <v>26559.28300236452</v>
       </c>
+      <c r="Q290" t="n">
+        <v>6.332900000000002</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -15257,6 +16127,9 @@
       <c r="P291" t="n">
         <v>27320.95315344946</v>
       </c>
+      <c r="Q291" t="n">
+        <v>8.493499999999997</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -15309,6 +16182,9 @@
       <c r="P292" t="n">
         <v>28253.61753425444</v>
       </c>
+      <c r="Q292" t="n">
+        <v>4.148099999999999</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -15361,6 +16237,9 @@
       <c r="P293" t="n">
         <v>28830.44592664971</v>
       </c>
+      <c r="Q293" t="n">
+        <v>5.923699999999997</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -15413,6 +16292,9 @@
       <c r="P294" t="n">
         <v>30433.05891198124</v>
       </c>
+      <c r="Q294" t="n">
+        <v>5.481800000000007</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -15465,6 +16347,9 @@
       <c r="P295" t="n">
         <v>31759.29923329489</v>
       </c>
+      <c r="Q295" t="n">
+        <v>8.344499999999996</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -15517,6 +16402,9 @@
       <c r="P296" t="n">
         <v>33083.3693943934</v>
       </c>
+      <c r="Q296" t="n">
+        <v>7.205300000000008</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -15569,6 +16457,9 @@
       <c r="P297" t="n">
         <v>32796.86101261676</v>
       </c>
+      <c r="Q297" t="n">
+        <v>5.44019999999999</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -15621,6 +16512,9 @@
       <c r="P298" t="n">
         <v>35111.85137503945</v>
       </c>
+      <c r="Q298" t="n">
+        <v>7.207899999999995</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -15673,6 +16567,9 @@
       <c r="P299" t="n">
         <v>35427.80718145795</v>
       </c>
+      <c r="Q299" t="n">
+        <v>6.142299999999992</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -15724,6 +16621,9 @@
       </c>
       <c r="P300" t="n">
         <v>34910.56337841541</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>5.447400000000002</v>
       </c>
     </row>
     <row r="301">
@@ -15765,6 +16665,7 @@
       <c r="P301" t="n">
         <v>35629.2832486382</v>
       </c>
+      <c r="Q301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -15816,6 +16717,9 @@
       </c>
       <c r="P302" t="n">
         <v>2937.975159818014</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>1.25475</v>
       </c>
     </row>
     <row r="303">
@@ -15863,6 +16767,9 @@
       <c r="P303" t="n">
         <v>3190.794718501618</v>
       </c>
+      <c r="Q303" t="n">
+        <v>1.22681</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -15915,6 +16822,9 @@
       <c r="P304" t="n">
         <v>3448.308747866785</v>
       </c>
+      <c r="Q304" t="n">
+        <v>3.18624</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -15967,6 +16877,9 @@
       <c r="P305" t="n">
         <v>3642.375517352661</v>
       </c>
+      <c r="Q305" t="n">
+        <v>6.12469</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -16019,6 +16932,9 @@
       <c r="P306" t="n">
         <v>4034.292470602131</v>
       </c>
+      <c r="Q306" t="n">
+        <v>9.141590000000001</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -16071,6 +16987,9 @@
       <c r="P307" t="n">
         <v>4339.413152942415</v>
       </c>
+      <c r="Q307" t="n">
+        <v>10.84306</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -16123,6 +17042,9 @@
       <c r="P308" t="n">
         <v>4278.543262914</v>
       </c>
+      <c r="Q308" t="n">
+        <v>12.21306</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -16175,6 +17097,9 @@
       <c r="P309" t="n">
         <v>4338.528673742751</v>
       </c>
+      <c r="Q309" t="n">
+        <v>9.820599999999999</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -16227,6 +17152,9 @@
       <c r="P310" t="n">
         <v>4606.09030101017</v>
       </c>
+      <c r="Q310" t="n">
+        <v>8.7597</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -16279,6 +17207,9 @@
       <c r="P311" t="n">
         <v>4240.074387577588</v>
       </c>
+      <c r="Q311" t="n">
+        <v>7.8794</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -16331,6 +17262,9 @@
       <c r="P312" t="n">
         <v>4340.653803834053</v>
       </c>
+      <c r="Q312" t="n">
+        <v>9.23</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -16383,6 +17317,9 @@
       <c r="P313" t="n">
         <v>4515.382437254404</v>
       </c>
+      <c r="Q313" t="n">
+        <v>8.68</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -16435,6 +17372,9 @@
       <c r="P314" t="n">
         <v>4460.715520027603</v>
       </c>
+      <c r="Q314" t="n">
+        <v>7.149999999999999</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -16487,6 +17427,9 @@
       <c r="P315" t="n">
         <v>4837.023668329169</v>
       </c>
+      <c r="Q315" t="n">
+        <v>7.759999999999998</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -16539,6 +17482,9 @@
       <c r="P316" t="n">
         <v>4805.791419359461</v>
       </c>
+      <c r="Q316" t="n">
+        <v>34.93</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -16591,6 +17537,9 @@
       <c r="P317" t="n">
         <v>4789.033515287651</v>
       </c>
+      <c r="Q317" t="n">
+        <v>34.35</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -16643,6 +17592,9 @@
       <c r="P318" t="n">
         <v>5122.905267484082</v>
       </c>
+      <c r="Q318" t="n">
+        <v>33.56</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -16695,6 +17647,9 @@
       <c r="P319" t="n">
         <v>5584.536729835335</v>
       </c>
+      <c r="Q319" t="n">
+        <v>-17.1</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -16747,6 +17702,9 @@
       <c r="P320" t="n">
         <v>6054.000637426012</v>
       </c>
+      <c r="Q320" t="n">
+        <v>-18.7</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -16799,6 +17757,9 @@
       <c r="P321" t="n">
         <v>6182.611888814402</v>
       </c>
+      <c r="Q321" t="n">
+        <v>-13.2395</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -16851,6 +17812,9 @@
       <c r="P322" t="n">
         <v>5720.100330978923</v>
       </c>
+      <c r="Q322" t="n">
+        <v>8.315300000000001</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -16903,6 +17867,9 @@
       <c r="P323" t="n">
         <v>6369.668825665569</v>
       </c>
+      <c r="Q323" t="n">
+        <v>24.19500000000001</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -16955,6 +17922,9 @@
       <c r="P324" t="n">
         <v>6236.205254887793</v>
       </c>
+      <c r="Q324" t="n">
+        <v>18.98070000000001</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -17006,6 +17976,9 @@
       </c>
       <c r="P325" t="n">
         <v>6652.725897501714</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>21.9973</v>
       </c>
     </row>
     <row r="326">
@@ -17047,6 +18020,7 @@
       <c r="P326" t="n">
         <v>6814.154018177316</v>
       </c>
+      <c r="Q326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -17092,6 +18066,9 @@
       </c>
       <c r="P327" t="n">
         <v>8129.106968579857</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>1.98157</v>
       </c>
     </row>
     <row r="328">
@@ -17133,6 +18110,9 @@
       <c r="P328" t="n">
         <v>7770.863355717945</v>
       </c>
+      <c r="Q328" t="n">
+        <v>2.46818</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -17179,6 +18159,9 @@
       <c r="P329" t="n">
         <v>7882.745357805757</v>
       </c>
+      <c r="Q329" t="n">
+        <v>15.83</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -17225,6 +18208,9 @@
       <c r="P330" t="n">
         <v>7942.081801705839</v>
       </c>
+      <c r="Q330" t="n">
+        <v>16.58443</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -17273,6 +18259,9 @@
       <c r="P331" t="n">
         <v>8315.078385475175</v>
       </c>
+      <c r="Q331" t="n">
+        <v>20.97182</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -17323,6 +18312,9 @@
       <c r="P332" t="n">
         <v>8717.805406607918</v>
       </c>
+      <c r="Q332" t="n">
+        <v>9.120000000000001</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -17373,6 +18365,9 @@
       <c r="P333" t="n">
         <v>9167.341062539919</v>
       </c>
+      <c r="Q333" t="n">
+        <v>9.550000000000001</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -17423,6 +18418,9 @@
       <c r="P334" t="n">
         <v>9582.529677324523</v>
       </c>
+      <c r="Q334" t="n">
+        <v>11.86</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -17473,6 +18471,9 @@
       <c r="P335" t="n">
         <v>10041.24734565125</v>
       </c>
+      <c r="Q335" t="n">
+        <v>19.59</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -17523,6 +18524,9 @@
       <c r="P336" t="n">
         <v>10024.26522787071</v>
       </c>
+      <c r="Q336" t="n">
+        <v>23.15</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -17573,6 +18577,9 @@
       <c r="P337" t="n">
         <v>10681.1053213769</v>
       </c>
+      <c r="Q337" t="n">
+        <v>15.6</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -17623,6 +18630,9 @@
       <c r="P338" t="n">
         <v>10672.96050049451</v>
       </c>
+      <c r="Q338" t="n">
+        <v>10.66</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -17673,6 +18683,9 @@
       <c r="P339" t="n">
         <v>10681.61587634451</v>
       </c>
+      <c r="Q339" t="n">
+        <v>5.679899999999996</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -17723,6 +18736,9 @@
       <c r="P340" t="n">
         <v>10927.90365763316</v>
       </c>
+      <c r="Q340" t="n">
+        <v>13.34</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -17773,6 +18789,9 @@
       <c r="P341" t="n">
         <v>11331.2968952854</v>
       </c>
+      <c r="Q341" t="n">
+        <v>11.35849999999999</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -17823,6 +18842,9 @@
       <c r="P342" t="n">
         <v>11890.98753964212</v>
       </c>
+      <c r="Q342" t="n">
+        <v>12.9303</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -17873,6 +18895,9 @@
       <c r="P343" t="n">
         <v>12358.65651364799</v>
       </c>
+      <c r="Q343" t="n">
+        <v>6.916800000000009</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -17923,6 +18948,9 @@
       <c r="P344" t="n">
         <v>12573.11098623322</v>
       </c>
+      <c r="Q344" t="n">
+        <v>6.458300000000008</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -17973,6 +19001,9 @@
       <c r="P345" t="n">
         <v>13059.32764005549</v>
       </c>
+      <c r="Q345" t="n">
+        <v>8.787599999999998</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -18023,6 +19054,9 @@
       <c r="P346" t="n">
         <v>13585.89089463034</v>
       </c>
+      <c r="Q346" t="n">
+        <v>9.256099999999989</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -18073,6 +19107,9 @@
       <c r="P347" t="n">
         <v>13314.6188796428</v>
       </c>
+      <c r="Q347" t="n">
+        <v>6.8887</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -18123,6 +19160,9 @@
       <c r="P348" t="n">
         <v>14194.42339859081</v>
       </c>
+      <c r="Q348" t="n">
+        <v>2.7059</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -18173,6 +19213,9 @@
       <c r="P349" t="n">
         <v>14263.49330599916</v>
       </c>
+      <c r="Q349" t="n">
+        <v>3.595100000000002</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -18222,6 +19265,9 @@
       </c>
       <c r="P350" t="n">
         <v>14660.18051546395</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>5.776399999999995</v>
       </c>
     </row>
     <row r="351">
@@ -18263,6 +19309,7 @@
       <c r="P351" t="n">
         <v>15411.42822605895</v>
       </c>
+      <c r="Q351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -18312,6 +19359,9 @@
       </c>
       <c r="P352" t="n">
         <v>16267.24157677211</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>5.21543</v>
       </c>
     </row>
     <row r="353">
@@ -18359,6 +19409,9 @@
       <c r="P353" t="n">
         <v>16307.827687315</v>
       </c>
+      <c r="Q353" t="n">
+        <v>5.80067</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -18411,6 +19464,9 @@
       <c r="P354" t="n">
         <v>16843.56202194501</v>
       </c>
+      <c r="Q354" t="n">
+        <v>15.69</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -18463,6 +19519,9 @@
       <c r="P355" t="n">
         <v>17521.6713874152</v>
       </c>
+      <c r="Q355" t="n">
+        <v>17.58457</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -18515,6 +19574,9 @@
       <c r="P356" t="n">
         <v>18448.33781097755</v>
       </c>
+      <c r="Q356" t="n">
+        <v>22.62933</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -18567,6 +19629,9 @@
       <c r="P357" t="n">
         <v>18748.53090493832</v>
       </c>
+      <c r="Q357" t="n">
+        <v>17.66</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -18619,6 +19684,9 @@
       <c r="P358" t="n">
         <v>20165.41971541894</v>
       </c>
+      <c r="Q358" t="n">
+        <v>19.71</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -18671,6 +19739,9 @@
       <c r="P359" t="n">
         <v>21541.39302754945</v>
       </c>
+      <c r="Q359" t="n">
+        <v>16.07</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -18723,6 +19794,9 @@
       <c r="P360" t="n">
         <v>22191.74786016762</v>
       </c>
+      <c r="Q360" t="n">
+        <v>14.32</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -18775,6 +19849,9 @@
       <c r="P361" t="n">
         <v>22382.0970016336</v>
       </c>
+      <c r="Q361" t="n">
+        <v>14.39</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -18827,6 +19904,9 @@
       <c r="P362" t="n">
         <v>22801.25743722405</v>
       </c>
+      <c r="Q362" t="n">
+        <v>13.72</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -18879,6 +19959,9 @@
       <c r="P363" t="n">
         <v>23909.09427140127</v>
       </c>
+      <c r="Q363" t="n">
+        <v>8.82</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -18931,6 +20014,9 @@
       <c r="P364" t="n">
         <v>24099.46381615056</v>
       </c>
+      <c r="Q364" t="n">
+        <v>3.340000000000003</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -18983,6 +20069,9 @@
       <c r="P365" t="n">
         <v>24217.05195404828</v>
       </c>
+      <c r="Q365" t="n">
+        <v>0.529200000000003</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -19035,6 +20124,9 @@
       <c r="P366" t="n">
         <v>24997.70133186545</v>
       </c>
+      <c r="Q366" t="n">
+        <v>4.648699999999991</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -19087,6 +20179,9 @@
       <c r="P367" t="n">
         <v>26178.79895849391</v>
       </c>
+      <c r="Q367" t="n">
+        <v>5.686999999999998</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -19139,6 +20234,9 @@
       <c r="P368" t="n">
         <v>26901.67127161039</v>
       </c>
+      <c r="Q368" t="n">
+        <v>10.4515</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -19191,6 +20289,9 @@
       <c r="P369" t="n">
         <v>28175.00978781267</v>
       </c>
+      <c r="Q369" t="n">
+        <v>9.386700000000005</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -19243,6 +20344,9 @@
       <c r="P370" t="n">
         <v>29978.05282051122</v>
       </c>
+      <c r="Q370" t="n">
+        <v>9.544700000000006</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -19295,6 +20399,9 @@
       <c r="P371" t="n">
         <v>31438.2752639219</v>
       </c>
+      <c r="Q371" t="n">
+        <v>7.135199999999998</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -19347,6 +20454,9 @@
       <c r="P372" t="n">
         <v>31233.50715606277</v>
       </c>
+      <c r="Q372" t="n">
+        <v>7.1995</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -19399,6 +20509,9 @@
       <c r="P373" t="n">
         <v>33202.09811709566</v>
       </c>
+      <c r="Q373" t="n">
+        <v>7.833199999999991</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -19451,6 +20564,9 @@
       <c r="P374" t="n">
         <v>34893.55793516013</v>
       </c>
+      <c r="Q374" t="n">
+        <v>6.505200000000002</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -19502,6 +20618,9 @@
       </c>
       <c r="P375" t="n">
         <v>34824.65311500178</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>3.229799999999997</v>
       </c>
     </row>
     <row r="376">
@@ -19545,6 +20664,9 @@
       <c r="P376" t="n">
         <v>36032.87450800207</v>
       </c>
+      <c r="Q376" t="n">
+        <v>3.210099999999997</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -19596,6 +20718,9 @@
       </c>
       <c r="P377" t="n">
         <v>10999.92659750571</v>
+      </c>
+      <c r="Q377" t="n">
+        <v>3.16872</v>
       </c>
     </row>
     <row r="378">
@@ -19643,6 +20768,9 @@
       <c r="P378" t="n">
         <v>11676.96133424187</v>
       </c>
+      <c r="Q378" t="n">
+        <v>2.29867</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -19695,6 +20823,9 @@
       <c r="P379" t="n">
         <v>12500.189728867</v>
       </c>
+      <c r="Q379" t="n">
+        <v>3.88</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -19747,6 +20878,9 @@
       <c r="P380" t="n">
         <v>12786.48508899839</v>
       </c>
+      <c r="Q380" t="n">
+        <v>5.286280000000001</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -19799,6 +20933,9 @@
       <c r="P381" t="n">
         <v>14139.89131333503</v>
       </c>
+      <c r="Q381" t="n">
+        <v>10.46133</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -19851,6 +20988,9 @@
       <c r="P382" t="n">
         <v>14835.89267923547</v>
       </c>
+      <c r="Q382" t="n">
+        <v>14.92</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -19903,6 +21043,9 @@
       <c r="P383" t="n">
         <v>16078.5361448817</v>
       </c>
+      <c r="Q383" t="n">
+        <v>15.76</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -19955,6 +21098,9 @@
       <c r="P384" t="n">
         <v>17457.33777315854</v>
       </c>
+      <c r="Q384" t="n">
+        <v>13.3</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -20007,6 +21153,9 @@
       <c r="P385" t="n">
         <v>19346.29321276494</v>
       </c>
+      <c r="Q385" t="n">
+        <v>10.92</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -20059,6 +21208,9 @@
       <c r="P386" t="n">
         <v>19869.81235839551</v>
       </c>
+      <c r="Q386" t="n">
+        <v>11.94</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -20111,6 +21263,9 @@
       <c r="P387" t="n">
         <v>18040.33986364829</v>
       </c>
+      <c r="Q387" t="n">
+        <v>11.63</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -20163,6 +21318,9 @@
       <c r="P388" t="n">
         <v>19083.34413745964</v>
       </c>
+      <c r="Q388" t="n">
+        <v>7.589999999999996</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -20215,6 +21373,9 @@
       <c r="P389" t="n">
         <v>19478.98128957101</v>
       </c>
+      <c r="Q389" t="n">
+        <v>9.280000000000001</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -20267,6 +21428,9 @@
       <c r="P390" t="n">
         <v>19582.11223932013</v>
       </c>
+      <c r="Q390" t="n">
+        <v>9.834499999999998</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -20319,6 +21483,9 @@
       <c r="P391" t="n">
         <v>20283.32764802832</v>
       </c>
+      <c r="Q391" t="n">
+        <v>14.0683</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -20371,6 +21538,9 @@
       <c r="P392" t="n">
         <v>20724.06924262111</v>
       </c>
+      <c r="Q392" t="n">
+        <v>9.883199999999995</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -20423,6 +21593,9 @@
       <c r="P393" t="n">
         <v>21592.59071309268</v>
       </c>
+      <c r="Q393" t="n">
+        <v>9.7395</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -20475,6 +21648,9 @@
       <c r="P394" t="n">
         <v>23126.96496329518</v>
       </c>
+      <c r="Q394" t="n">
+        <v>9.669000000000004</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -20527,6 +21703,9 @@
       <c r="P395" t="n">
         <v>24729.23177772817</v>
       </c>
+      <c r="Q395" t="n">
+        <v>14.9181</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -20579,6 +21758,9 @@
       <c r="P396" t="n">
         <v>25779.74000470067</v>
       </c>
+      <c r="Q396" t="n">
+        <v>14.1535</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -20631,6 +21813,9 @@
       <c r="P397" t="n">
         <v>25007.45761964777</v>
       </c>
+      <c r="Q397" t="n">
+        <v>14.70799999999999</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -20683,6 +21868,9 @@
       <c r="P398" t="n">
         <v>26366.75208268217</v>
       </c>
+      <c r="Q398" t="n">
+        <v>12.90910000000001</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -20735,6 +21923,9 @@
       <c r="P399" t="n">
         <v>27422.75736870142</v>
       </c>
+      <c r="Q399" t="n">
+        <v>11.8456</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -20786,6 +21977,9 @@
       </c>
       <c r="P400" t="n">
         <v>28540.79842029152</v>
+      </c>
+      <c r="Q400" t="n">
+        <v>10.74810000000001</v>
       </c>
     </row>
     <row r="401">
@@ -20831,6 +22025,9 @@
       <c r="P401" t="n">
         <v>28832.29048360474</v>
       </c>
+      <c r="Q401" t="n">
+        <v>7.700099999999992</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -20875,6 +22072,7 @@
       <c r="P402" t="n">
         <v>7677.5248462297</v>
       </c>
+      <c r="Q402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -20913,6 +22111,7 @@
       <c r="P403" t="n">
         <v>8228.236277611686</v>
       </c>
+      <c r="Q403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -20957,6 +22156,7 @@
       <c r="P404" t="n">
         <v>8787.548117865486</v>
       </c>
+      <c r="Q404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -21003,6 +22203,7 @@
       <c r="P405" t="n">
         <v>9227.518429383477</v>
       </c>
+      <c r="Q405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -21051,6 +22252,7 @@
       <c r="P406" t="n">
         <v>9915.973703428506</v>
       </c>
+      <c r="Q406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -21099,6 +22301,7 @@
       <c r="P407" t="n">
         <v>10567.23752757426</v>
       </c>
+      <c r="Q407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -21147,6 +22350,7 @@
       <c r="P408" t="n">
         <v>11054.38514016686</v>
       </c>
+      <c r="Q408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -21199,6 +22403,9 @@
       <c r="P409" t="n">
         <v>11923.95887486237</v>
       </c>
+      <c r="Q409" t="n">
+        <v>9.649999999999999</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -21251,6 +22458,9 @@
       <c r="P410" t="n">
         <v>12740.31783111772</v>
       </c>
+      <c r="Q410" t="n">
+        <v>9.300000000000001</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -21303,6 +22513,9 @@
       <c r="P411" t="n">
         <v>12814.55380789496</v>
       </c>
+      <c r="Q411" t="n">
+        <v>10.9</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -21355,6 +22568,9 @@
       <c r="P412" t="n">
         <v>13398.50845486902</v>
       </c>
+      <c r="Q412" t="n">
+        <v>7.75</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -21407,6 +22623,9 @@
       <c r="P413" t="n">
         <v>13465.54504785048</v>
       </c>
+      <c r="Q413" t="n">
+        <v>6.600000000000001</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -21459,6 +22678,9 @@
       <c r="P414" t="n">
         <v>13354.682037168</v>
       </c>
+      <c r="Q414" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -21511,6 +22733,9 @@
       <c r="P415" t="n">
         <v>13216.01309403173</v>
       </c>
+      <c r="Q415" t="n">
+        <v>12.5504</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -21563,6 +22788,9 @@
       <c r="P416" t="n">
         <v>12929.57943880975</v>
       </c>
+      <c r="Q416" t="n">
+        <v>19.8751</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -21615,6 +22843,9 @@
       <c r="P417" t="n">
         <v>13265.34198781202</v>
       </c>
+      <c r="Q417" t="n">
+        <v>17.21699999999999</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -21667,6 +22898,9 @@
       <c r="P418" t="n">
         <v>13276.87316481708</v>
       </c>
+      <c r="Q418" t="n">
+        <v>13.60639999999999</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -21719,6 +22953,9 @@
       <c r="P419" t="n">
         <v>13508.60728476362</v>
       </c>
+      <c r="Q419" t="n">
+        <v>8.255699999999997</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -21771,6 +23008,9 @@
       <c r="P420" t="n">
         <v>14102.20716101458</v>
       </c>
+      <c r="Q420" t="n">
+        <v>8.043700000000001</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -21823,6 +23063,9 @@
       <c r="P421" t="n">
         <v>14821.33135427807</v>
       </c>
+      <c r="Q421" t="n">
+        <v>10.36</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -21875,6 +23118,9 @@
       <c r="P422" t="n">
         <v>14971.03488661722</v>
       </c>
+      <c r="Q422" t="n">
+        <v>8.037199999999999</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -21927,6 +23173,9 @@
       <c r="P423" t="n">
         <v>15355.66718619577</v>
       </c>
+      <c r="Q423" t="n">
+        <v>7.805199999999999</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -21978,6 +23227,9 @@
       </c>
       <c r="P424" t="n">
         <v>15917.4562155314</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>6.121500000000012</v>
       </c>
     </row>
     <row r="425">
@@ -22028,6 +23280,9 @@
       </c>
       <c r="P425" t="n">
         <v>16750.59989037223</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>6.989500000000007</v>
       </c>
     </row>
     <row r="426">
@@ -22071,6 +23326,9 @@
       <c r="P426" t="n">
         <v>17491.49875385929</v>
       </c>
+      <c r="Q426" t="n">
+        <v>6.524800000000013</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -22122,6 +23380,9 @@
       </c>
       <c r="P427" t="n">
         <v>18778.01201458407</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>8.2568</v>
       </c>
     </row>
     <row r="428">
@@ -22169,6 +23430,9 @@
       <c r="P428" t="n">
         <v>19037.14035489135</v>
       </c>
+      <c r="Q428" t="n">
+        <v>9.8383</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -22221,6 +23485,9 @@
       <c r="P429" t="n">
         <v>19824.46087560963</v>
       </c>
+      <c r="Q429" t="n">
+        <v>34.7</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -22273,6 +23540,9 @@
       <c r="P430" t="n">
         <v>20526.26563711752</v>
       </c>
+      <c r="Q430" t="n">
+        <v>33.6132</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -22325,6 +23595,9 @@
       <c r="P431" t="n">
         <v>21584.7818972917</v>
       </c>
+      <c r="Q431" t="n">
+        <v>40.3617</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -22377,6 +23650,9 @@
       <c r="P432" t="n">
         <v>23088.61617058487</v>
       </c>
+      <c r="Q432" t="n">
+        <v>15.05</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -22429,6 +23705,9 @@
       <c r="P433" t="n">
         <v>25185.64289954992</v>
       </c>
+      <c r="Q433" t="n">
+        <v>13.04</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -22481,6 +23760,9 @@
       <c r="P434" t="n">
         <v>27933.08397874395</v>
       </c>
+      <c r="Q434" t="n">
+        <v>8.909999999999997</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -22533,6 +23815,9 @@
       <c r="P435" t="n">
         <v>29071.04515458599</v>
       </c>
+      <c r="Q435" t="n">
+        <v>10.86</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -22585,6 +23870,9 @@
       <c r="P436" t="n">
         <v>27591.81460286949</v>
       </c>
+      <c r="Q436" t="n">
+        <v>13.92</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -22637,6 +23925,9 @@
       <c r="P437" t="n">
         <v>29345.9535973756</v>
       </c>
+      <c r="Q437" t="n">
+        <v>13.91</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -22689,6 +23980,9 @@
       <c r="P438" t="n">
         <v>30064.22039176654</v>
       </c>
+      <c r="Q438" t="n">
+        <v>8.390000000000001</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -22741,6 +24035,9 @@
       <c r="P439" t="n">
         <v>30272.51902349094</v>
       </c>
+      <c r="Q439" t="n">
+        <v>6.709999999999994</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -22793,6 +24090,9 @@
       <c r="P440" t="n">
         <v>30404.31251435996</v>
       </c>
+      <c r="Q440" t="n">
+        <v>2.172600000000003</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -22845,6 +24145,9 @@
       <c r="P441" t="n">
         <v>30910.28943902251</v>
       </c>
+      <c r="Q441" t="n">
+        <v>5.544300000000007</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -22897,6 +24200,9 @@
       <c r="P442" t="n">
         <v>32569.86902716198</v>
       </c>
+      <c r="Q442" t="n">
+        <v>0.9247000000000014</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -22949,6 +24255,9 @@
       <c r="P443" t="n">
         <v>32978.222837149</v>
       </c>
+      <c r="Q443" t="n">
+        <v>2.593299999999999</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -23001,6 +24310,9 @@
       <c r="P444" t="n">
         <v>33993.81886431856</v>
       </c>
+      <c r="Q444" t="n">
+        <v>1.64139999999999</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -23053,6 +24365,9 @@
       <c r="P445" t="n">
         <v>35484.19673665798</v>
       </c>
+      <c r="Q445" t="n">
+        <v>2.8142</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -23105,6 +24420,9 @@
       <c r="P446" t="n">
         <v>36393.07114396051</v>
       </c>
+      <c r="Q446" t="n">
+        <v>2.377800000000008</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -23157,6 +24475,9 @@
       <c r="P447" t="n">
         <v>35838.34568124945</v>
       </c>
+      <c r="Q447" t="n">
+        <v>8.295200000000008</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -23209,6 +24530,9 @@
       <c r="P448" t="n">
         <v>37176.47843236282</v>
       </c>
+      <c r="Q448" t="n">
+        <v>8.476700000000008</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -23261,6 +24585,9 @@
       <c r="P449" t="n">
         <v>36878.74294052779</v>
       </c>
+      <c r="Q449" t="n">
+        <v>6.213999999999999</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -23312,6 +24639,9 @@
       </c>
       <c r="P450" t="n">
         <v>37663.52782420043</v>
+      </c>
+      <c r="Q450" t="n">
+        <v>-2.707800000000006</v>
       </c>
     </row>
     <row r="451">
@@ -23355,6 +24685,9 @@
       <c r="P451" t="n">
         <v>38621.68935549439</v>
       </c>
+      <c r="Q451" t="n">
+        <v>0.8995000000000033</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -23406,6 +24739,9 @@
       </c>
       <c r="P452" t="n">
         <v>33269.19697492829</v>
+      </c>
+      <c r="Q452" t="n">
+        <v>7.520300000000001</v>
       </c>
     </row>
     <row r="453">
@@ -23453,6 +24789,9 @@
       <c r="P453" t="n">
         <v>33980.01508946986</v>
       </c>
+      <c r="Q453" t="n">
+        <v>20.0759</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -23505,6 +24844,9 @@
       <c r="P454" t="n">
         <v>34546.1059543543</v>
       </c>
+      <c r="Q454" t="n">
+        <v>15.2389</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -23557,6 +24899,9 @@
       <c r="P455" t="n">
         <v>36507.09867269693</v>
       </c>
+      <c r="Q455" t="n">
+        <v>16.7445</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -23609,6 +24954,9 @@
       <c r="P456" t="n">
         <v>36469.71804390542</v>
       </c>
+      <c r="Q456" t="n">
+        <v>10.6341</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -23661,6 +25009,9 @@
       <c r="P457" t="n">
         <v>37547.95957308051</v>
       </c>
+      <c r="Q457" t="n">
+        <v>18.9711</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -23713,6 +25064,9 @@
       <c r="P458" t="n">
         <v>39471.86451773466</v>
       </c>
+      <c r="Q458" t="n">
+        <v>22.1552</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -23765,6 +25119,9 @@
       <c r="P459" t="n">
         <v>41626.27708905109</v>
       </c>
+      <c r="Q459" t="n">
+        <v>15.93</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -23817,6 +25174,9 @@
       <c r="P460" t="n">
         <v>43107.73216849934</v>
       </c>
+      <c r="Q460" t="n">
+        <v>11.19</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -23869,6 +25229,9 @@
       <c r="P461" t="n">
         <v>39606.63851856717</v>
       </c>
+      <c r="Q461" t="n">
+        <v>9.990000000000002</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -23921,6 +25284,9 @@
       <c r="P462" t="n">
         <v>40110.36372671415</v>
       </c>
+      <c r="Q462" t="n">
+        <v>13.26</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -23973,6 +25339,9 @@
       <c r="P463" t="n">
         <v>41190.88175651777</v>
       </c>
+      <c r="Q463" t="n">
+        <v>9.340000000000003</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -24025,6 +25394,9 @@
       <c r="P464" t="n">
         <v>40199.73740567388</v>
       </c>
+      <c r="Q464" t="n">
+        <v>4.349999999999994</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -24077,6 +25449,9 @@
       <c r="P465" t="n">
         <v>40022.40658306058</v>
       </c>
+      <c r="Q465" t="n">
+        <v>2.675600000000003</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -24129,6 +25504,9 @@
       <c r="P466" t="n">
         <v>40993.80022744944</v>
       </c>
+      <c r="Q466" t="n">
+        <v>4.246299999999991</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -24181,6 +25559,9 @@
       <c r="P467" t="n">
         <v>42192.85891031574</v>
       </c>
+      <c r="Q467" t="n">
+        <v>4.748699999999999</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -24233,6 +25614,9 @@
       <c r="P468" t="n">
         <v>44061.49695373116</v>
       </c>
+      <c r="Q468" t="n">
+        <v>2.822900000000004</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -24285,6 +25669,9 @@
       <c r="P469" t="n">
         <v>45010.47373312982</v>
       </c>
+      <c r="Q469" t="n">
+        <v>7.29910000000001</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -24337,6 +25724,9 @@
       <c r="P470" t="n">
         <v>46538.87875555225</v>
       </c>
+      <c r="Q470" t="n">
+        <v>6.651300000000006</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -24389,6 +25779,9 @@
       <c r="P471" t="n">
         <v>48308.77586335252</v>
       </c>
+      <c r="Q471" t="n">
+        <v>7.609899999999996</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -24441,6 +25834,9 @@
       <c r="P472" t="n">
         <v>46498.29836101083</v>
       </c>
+      <c r="Q472" t="n">
+        <v>7.715899999999991</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -24493,6 +25889,9 @@
       <c r="P473" t="n">
         <v>49788.23473974447</v>
       </c>
+      <c r="Q473" t="n">
+        <v>9.254000000000005</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -24545,6 +25944,9 @@
       <c r="P474" t="n">
         <v>50414.4731804961</v>
       </c>
+      <c r="Q474" t="n">
+        <v>5.804099999999991</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -24596,6 +25998,9 @@
       </c>
       <c r="P475" t="n">
         <v>51503.59967118113</v>
+      </c>
+      <c r="Q475" t="n">
+        <v>3.776600000000002</v>
       </c>
     </row>
     <row r="476">
@@ -24641,6 +26046,9 @@
       <c r="P476" t="n">
         <v>52331.78067316607</v>
       </c>
+      <c r="Q476" t="n">
+        <v>1.759599999999992</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -24690,6 +26098,9 @@
       </c>
       <c r="P477" t="n">
         <v>12027.87571466159</v>
+      </c>
+      <c r="Q477" t="n">
+        <v>3.28769</v>
       </c>
     </row>
     <row r="478">
@@ -24735,6 +26146,9 @@
       <c r="P478" t="n">
         <v>8693.600041241509</v>
       </c>
+      <c r="Q478" t="n">
+        <v>4.49048</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -24785,6 +26199,9 @@
       <c r="P479" t="n">
         <v>10206.96585821972</v>
       </c>
+      <c r="Q479" t="n">
+        <v>9.09</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -24835,6 +26252,9 @@
       <c r="P480" t="n">
         <v>13464.01913414556</v>
       </c>
+      <c r="Q480" t="n">
+        <v>8.56831</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -24885,6 +26305,9 @@
       <c r="P481" t="n">
         <v>17952.08255707089</v>
       </c>
+      <c r="Q481" t="n">
+        <v>9.39052</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -24935,6 +26358,9 @@
       <c r="P482" t="n">
         <v>21812.05370053612</v>
       </c>
+      <c r="Q482" t="n">
+        <v>4.08</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -24985,6 +26411,9 @@
       <c r="P483" t="n">
         <v>23708.19120393481</v>
       </c>
+      <c r="Q483" t="n">
+        <v>5.909999999999998</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -25035,6 +26464,9 @@
       <c r="P484" t="n">
         <v>28826.52900663274</v>
       </c>
+      <c r="Q484" t="n">
+        <v>14.05</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -25087,6 +26519,9 @@
       <c r="P485" t="n">
         <v>31568.70187652872</v>
       </c>
+      <c r="Q485" t="n">
+        <v>18.91</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -25139,6 +26574,9 @@
       <c r="P486" t="n">
         <v>25548.83883193543</v>
       </c>
+      <c r="Q486" t="n">
+        <v>18.16</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -25191,6 +26629,9 @@
       <c r="P487" t="n">
         <v>29371.9567388243</v>
       </c>
+      <c r="Q487" t="n">
+        <v>11.19</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -25243,6 +26684,9 @@
       <c r="P488" t="n">
         <v>30417.92928651552</v>
       </c>
+      <c r="Q488" t="n">
+        <v>8.695700000000002</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -25295,6 +26739,9 @@
       <c r="P489" t="n">
         <v>31306.99735751825</v>
       </c>
+      <c r="Q489" t="n">
+        <v>8.730000000000004</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -25347,6 +26794,9 @@
       <c r="P490" t="n">
         <v>32857.93076041756</v>
       </c>
+      <c r="Q490" t="n">
+        <v>6.43</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -25399,6 +26849,9 @@
       <c r="P491" t="n">
         <v>31804.65936148346</v>
       </c>
+      <c r="Q491" t="n">
+        <v>7.971699999999998</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -25451,6 +26904,9 @@
       <c r="P492" t="n">
         <v>28290.94245626559</v>
       </c>
+      <c r="Q492" t="n">
+        <v>8.614999999999995</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -25503,6 +26959,9 @@
       <c r="P493" t="n">
         <v>27596.54527712311</v>
       </c>
+      <c r="Q493" t="n">
+        <v>12.0977</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -25555,6 +27014,9 @@
       <c r="P494" t="n">
         <v>26401.68931439679</v>
       </c>
+      <c r="Q494" t="n">
+        <v>13.64720000000001</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -25607,6 +27069,9 @@
       <c r="P495" t="n">
         <v>23390.77163605544</v>
       </c>
+      <c r="Q495" t="n">
+        <v>17.2978</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -25659,6 +27124,9 @@
       <c r="P496" t="n">
         <v>22591.02817058313</v>
       </c>
+      <c r="Q496" t="n">
+        <v>15.62899999999999</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -25711,6 +27179,9 @@
       <c r="P497" t="n">
         <v>22673.43972316802</v>
       </c>
+      <c r="Q497" t="n">
+        <v>12.985</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -25763,6 +27234,9 @@
       <c r="P498" t="n">
         <v>24480.38993926208</v>
       </c>
+      <c r="Q498" t="n">
+        <v>10.3656</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -25815,6 +27289,9 @@
       <c r="P499" t="n">
         <v>25857.389337939</v>
       </c>
+      <c r="Q499" t="n">
+        <v>9.46050000000001</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -25866,6 +27343,9 @@
       </c>
       <c r="P500" t="n">
         <v>31451.37800022971</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>8.2911</v>
       </c>
     </row>
     <row r="501">
@@ -25910,6 +27390,9 @@
       </c>
       <c r="P501" t="n">
         <v>36674.74625252372</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>5.899500000000003</v>
       </c>
     </row>
   </sheetData>
